--- a/web/files/港岛-半山区东部-肇辉台6号.xlsx
+++ b/web/files/港岛-半山区东部-肇辉台6号.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>110000000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>40786</v>
+        <v>39216</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>110000000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40786</v>
+        <v>39216</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>118000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>43639</v>
+        <v>41903</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>118000000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>43639</v>
+        <v>41903</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>158783000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>58874</v>
+        <v>56607</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>147271232</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>54606</v>
+        <v>52503</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>152207000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>56290</v>
+        <v>54051</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>141171992</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>52209</v>
+        <v>50132</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>135916000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>50265</v>
+        <v>48266</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>126062090</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>46621</v>
+        <v>44766</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>149386000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>55390</v>
+        <v>53257</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>138555515</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>51374</v>
+        <v>49396</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>144848000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>53568</v>
+        <v>51438</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>134346520</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>49684</v>
+        <v>47708</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>146541000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>54335</v>
+        <v>52243</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135916778</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>50396</v>
+        <v>48455</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>130548000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>48280</v>
+        <v>46359</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>121083270</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>44779</v>
+        <v>42998</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>88656000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>32872</v>
+        <v>31606</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>88656000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>32872</v>
+        <v>31606</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129613000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>47934</v>
+        <v>46027</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>120216058</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>44459</v>
+        <v>42690</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>156655000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>58085</v>
+        <v>55848</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>145297512</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>53874</v>
+        <v>51799</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128678000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>47588</v>
+        <v>45695</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>119348845</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>44138</v>
+        <v>42382</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>85785000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>31808</v>
+        <v>30583</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>85785000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>31808</v>
+        <v>30583</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2800</v>
+        <v>2816</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2697</v>
+        <v>2805</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>126841000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>46909</v>
+        <v>45043</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>117645028</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>43508</v>
+        <v>41777</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>125928000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>46571</v>
+        <v>44719</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>116798220</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>43195</v>
+        <v>41477</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2776</v>
+        <v>2805</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>74987000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>27013</v>
+        <v>26733</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>74987000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>27013</v>
+        <v>26733</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>125015000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>46233</v>
+        <v>44395</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>115951412</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>42881</v>
+        <v>41176</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2704</v>
+        <v>2816</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>122000000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>45118</v>
+        <v>43324</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>122000000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>45118</v>
+        <v>43324</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $11800万
-$43,639/呎
+$41,903/呎
 (23年-07月-14日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $11000万
-$40,786/呎
+$39,216/呎
 (12年-12月-03日)</t>
         </is>
       </c>
@@ -2394,17 +2394,17 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $15221万
-$56,290/呎
+$54,051/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $15878万
-$58,874/呎
+$56,607/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -2417,15 +2417,15 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $13592万
-$50,265/呎
+$48,266/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 -
 -
 (待售)</t>
@@ -2440,17 +2440,17 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $14485万
-$53,568/呎
+$51,438/呎
 (暂停销售)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $14939万
-$55,390/呎
+$53,257/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -2463,17 +2463,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $13055万
-$48,280/呎
+$46,359/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $14654万
-$54,335/呎
+$52,243/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $12961万
-$47,934/呎
+$46,027/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $8866万
-$32,872/呎
+$31,606/呎
 (14年-10月-08日)</t>
         </is>
       </c>
@@ -2509,17 +2509,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $12868万
-$47,588/呎
+$45,695/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $15666万
-$58,085/呎
+$55,848/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 2800呎 (4+房)
+          <t>A | 2816呎 (4+房)
 -
 -
 (待售)</t>
@@ -2540,9 +2540,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $8578万
-$31,808/呎
+$30,583/呎
 (14年-10月-29日)</t>
         </is>
       </c>
@@ -2555,15 +2555,15 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $12684万
-$46,909/呎
+$45,043/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 2697呎 (4+房)
+          <t>B | 2805呎 (4+房)
 -
 -
 (待售)</t>
@@ -2578,9 +2578,9 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $12593万
-$46,571/呎
+$44,719/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -2601,17 +2601,17 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $12502万
-$46,233/呎
+$44,395/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 2776呎 (4+房)
+          <t>B | 2805呎 (4+房)
 $7499万
-$27,013/呎
+$26,733/呎
 (11年-06月-02日)</t>
         </is>
       </c>
@@ -2624,9 +2624,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 2704呎 (4+房)
+          <t>A | 2816呎 (4+房)
 $12200万
-$45,118/呎
+$43,324/呎
 (12年-12月-03日)</t>
         </is>
       </c>
